--- a/セリフ編集/その他セリフ/08-成長・スランプ・モチベーション.xlsx
+++ b/セリフ編集/その他セリフ/08-成長・スランプ・モチベーション.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I169"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4704,7 +4704,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.normal._default[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">fresh.normal._default[1]</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="5">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…やれる。やってみせる</t>
+          <t xml:space="preserve">今日は体が軽い。なんでもできそうな気がする</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal._default[2]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.bold._default[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4746,29 +4746,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fresh.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また闘いたいと思えた。この気持ちを大切に</t>
+          <t xml:space="preserve">体が動きたがってる。もっとやらせてくれない?</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.easygoing._default[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4778,29 +4778,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">fresh.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと目が覚めた。ここで終わるわけにはいかない！</t>
+          <t xml:space="preserve">なんか今日、体が軽いんだよねー。いけるいける</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.earnest._default[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4810,29 +4810,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">fresh.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう一度、闘える</t>
+          <t xml:space="preserve">体が素直に動きます。やった分だけ返ってきます</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.shy._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.emotional._default[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4842,29 +4842,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">fresh.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ自信はないですけど…もう少しだけ、頑張ってみます</t>
+          <t xml:space="preserve">体が軽い…!今ならなんでもできる気がする…!</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.quiet._default[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4874,29 +4874,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">fresh.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、またやる気出てきたぞ！ 楽しまなきゃね</t>
+          <t xml:space="preserve">…体が、軽いです。…今日は、いけます</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.shy._default[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4906,59 +4906,731 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">fresh.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘うことを忘れていた…でも、もう迷わない</t>
+          <t xml:space="preserve">な、なんだか今日、体が軽くて…!やれそうです…!</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">warm.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">同じだけやってるのに、手応えが薄い気がする</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">warm.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだやれる。…切れが鈍った? 気のせいだって</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">warm.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">んー、なんか乗り切らないなー。動けてはいるけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">warm.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">同じだけやってるのに、身についてる感じがしません</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="A152" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">warm.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あれ…なんか入ってこない…!?もっとやれるはずなのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">warm.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…同じことを、しているのに。…返るものが、少ない</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="A154" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">warm.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの…同じようにやってるはずなんですけど…なんだか…</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="A155" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heavy.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">体が重い。動いてはいるけど、何も残らないな</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="A156" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heavy.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">重い。…でも止まらない。止まったら負けた気がする</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="40" customHeight="1">
+      <c r="A157" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heavy.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あー、体が重い。今日は何やっても身にならないねー</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="40" customHeight="1">
+      <c r="A158" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heavy.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">動きが同じところで止まる。私の集中が足りないのかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="40" customHeight="1">
+      <c r="A159" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heavy.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">体が重い…!やる気はあるのに、体がついてこない…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="40" customHeight="1">
+      <c r="A160" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heavy.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…体が、重いです。…今日は、たぶん、残りません</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="40" customHeight="1">
+      <c r="A161" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heavy.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…体が重いです…今日は、身になってない気がして…</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ…やれる。やってみせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="40" customHeight="1">
+      <c r="A163" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">また闘いたいと思えた。この気持ちを大切に</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やっと目が覚めた。ここで終わるわけにはいかない！</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="40" customHeight="1">
+      <c r="A165" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう一度、闘える</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="40" customHeight="1">
+      <c r="A166" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ自信はないですけど…もう少しだけ、頑張ってみます</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="40" customHeight="1">
+      <c r="A167" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よーし、またやる気出てきたぞ！ 楽しまなきゃね</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">闘うことを忘れていた…でも、もう迷わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.emotional._default[1]</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr" s="2">
+      <c r="B169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr" s="12">
+      <c r="D169" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">emotional._default[1]</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr" s="10">
+      <c r="F169" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">感情的</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr" s="3">
+      <c r="G169" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うっ…また闘いたいって…思えたよ…！ 大丈夫、もう大丈夫…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I148"/>
+  <autoFilter ref="A1:I169"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/その他セリフ/08-成長・スランプ・モチベーション.xlsx
+++ b/セリフ編集/その他セリフ/08-成長・スランプ・モチベーション.xlsx
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal._default[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -288,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal._default[2]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -303,7 +303,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="5">
@@ -320,7 +320,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold._default[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="6">
@@ -352,7 +352,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold._default[2]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="6">
@@ -384,7 +384,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="7">
@@ -416,7 +416,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="7">
@@ -448,7 +448,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="9">
@@ -480,7 +480,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="9">
@@ -512,7 +512,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="10">
@@ -544,7 +544,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="10">
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="10">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">BT_HINT_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="10">
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal._default[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="5">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal._default[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="5">
@@ -704,7 +704,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold._default[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="6">
@@ -736,7 +736,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold._default[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="6">
@@ -768,7 +768,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="7">
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.shy._default[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="8">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="9">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="10">
@@ -896,7 +896,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="10">
@@ -928,7 +928,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="10">
@@ -960,7 +960,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="10">
@@ -992,7 +992,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.normal[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal._default[1]</t>
+          <t xml:space="preserve">ovr_growth._default.normal[1]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="5">
@@ -1024,7 +1024,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.normal[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal._default[2]</t>
+          <t xml:space="preserve">ovr_growth._default.normal[2]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="5">
@@ -1056,7 +1056,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.bold[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold._default[1]</t>
+          <t xml:space="preserve">ovr_growth._default.bold[1]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="6">
@@ -1088,7 +1088,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.bold[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold._default[2]</t>
+          <t xml:space="preserve">ovr_growth._default.bold[2]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="6">
@@ -1120,7 +1120,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.quiet._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.quiet[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.quiet._default[1]</t>
+          <t xml:space="preserve">ovr_growth._default.quiet[1]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="7">
@@ -1152,7 +1152,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.easygoing._default[1]</t>
+          <t xml:space="preserve">ovr_growth._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="9">
@@ -1184,7 +1184,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.easygoing._default[2]</t>
+          <t xml:space="preserve">ovr_growth._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="9">
@@ -1216,7 +1216,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.earnest[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.earnest._default[1]</t>
+          <t xml:space="preserve">ovr_growth._default.earnest[1]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="10">
@@ -1248,7 +1248,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.earnest[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.earnest._default[2]</t>
+          <t xml:space="preserve">ovr_growth._default.earnest[2]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="10">
@@ -1280,7 +1280,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.emotional._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.emotional[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.emotional._default[1]</t>
+          <t xml:space="preserve">ovr_growth._default.emotional[1]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="10">
@@ -1312,7 +1312,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.emotional._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth._default.emotional[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.emotional._default[2]</t>
+          <t xml:space="preserve">ovr_growth._default.emotional[2]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="10">
@@ -1344,7 +1344,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.normal[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal._default[1]</t>
+          <t xml:space="preserve">ovr_elite._default.normal[1]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="5">
@@ -1376,7 +1376,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.normal[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal._default[2]</t>
+          <t xml:space="preserve">ovr_elite._default.normal[2]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="5">
@@ -1408,7 +1408,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.bold[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold._default[1]</t>
+          <t xml:space="preserve">ovr_elite._default.bold[1]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="6">
@@ -1440,7 +1440,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.bold[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold._default[2]</t>
+          <t xml:space="preserve">ovr_elite._default.bold[2]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="6">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.quiet._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.quiet[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.quiet._default[1]</t>
+          <t xml:space="preserve">ovr_elite._default.quiet[1]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="7">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.easygoing._default[1]</t>
+          <t xml:space="preserve">ovr_elite._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="9">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.earnest._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.earnest[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.earnest._default[1]</t>
+          <t xml:space="preserve">ovr_elite._default.earnest[1]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="10">
@@ -1568,7 +1568,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.earnest._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.earnest[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.earnest._default[2]</t>
+          <t xml:space="preserve">ovr_elite._default.earnest[2]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="10">
@@ -1600,7 +1600,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.emotional._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.emotional[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.emotional._default[1]</t>
+          <t xml:space="preserve">ovr_elite._default.emotional[1]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="10">
@@ -1632,7 +1632,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.emotional._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite._default.emotional[2]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.emotional._default[2]</t>
+          <t xml:space="preserve">ovr_elite._default.emotional[2]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="10">
@@ -1664,7 +1664,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.normal[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal._default[1]</t>
+          <t xml:space="preserve">ovr_legend._default.normal[1]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="5">
@@ -1696,7 +1696,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.normal[2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal._default[2]</t>
+          <t xml:space="preserve">ovr_legend._default.normal[2]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="5">
@@ -1728,7 +1728,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.bold[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold._default[1]</t>
+          <t xml:space="preserve">ovr_legend._default.bold[1]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="6">
@@ -1760,7 +1760,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.bold[2]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold._default[2]</t>
+          <t xml:space="preserve">ovr_legend._default.bold[2]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="6">
@@ -1792,7 +1792,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.quiet._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.quiet[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.quiet._default[1]</t>
+          <t xml:space="preserve">ovr_legend._default.quiet[1]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="7">
@@ -1824,7 +1824,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.easygoing._default[1]</t>
+          <t xml:space="preserve">ovr_legend._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="9">
@@ -1856,7 +1856,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.earnest._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.earnest[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.earnest._default[1]</t>
+          <t xml:space="preserve">ovr_legend._default.earnest[1]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="10">
@@ -1888,7 +1888,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.earnest._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.earnest[2]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.earnest._default[2]</t>
+          <t xml:space="preserve">ovr_legend._default.earnest[2]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="10">
@@ -1920,7 +1920,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.emotional._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.emotional[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.emotional._default[1]</t>
+          <t xml:space="preserve">ovr_legend._default.emotional[1]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="10">
@@ -1952,7 +1952,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.emotional._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend._default.emotional[2]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.emotional._default[2]</t>
+          <t xml:space="preserve">ovr_legend._default.emotional[2]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="10">
@@ -1984,7 +1984,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.normal[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal._default[1]</t>
+          <t xml:space="preserve">pop_growth._default.normal[1]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="5">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.normal[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal._default[2]</t>
+          <t xml:space="preserve">pop_growth._default.normal[2]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="5">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.bold[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.bold._default[1]</t>
+          <t xml:space="preserve">pop_growth._default.bold[1]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="6">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.bold[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.bold._default[2]</t>
+          <t xml:space="preserve">pop_growth._default.bold[2]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="6">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.quiet._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.quiet[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.quiet._default[1]</t>
+          <t xml:space="preserve">pop_growth._default.quiet[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="7">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.easygoing._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.easygoing._default[1]</t>
+          <t xml:space="preserve">pop_growth._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="9">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.easygoing._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.easygoing._default[2]</t>
+          <t xml:space="preserve">pop_growth._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="9">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.earnest._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.earnest[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.earnest._default[1]</t>
+          <t xml:space="preserve">pop_growth._default.earnest[1]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="10">
@@ -2240,7 +2240,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.earnest._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.earnest[2]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.earnest._default[2]</t>
+          <t xml:space="preserve">pop_growth._default.earnest[2]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="10">
@@ -2272,7 +2272,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.emotional._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.emotional[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.emotional._default[1]</t>
+          <t xml:space="preserve">pop_growth._default.emotional[1]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="10">
@@ -2304,7 +2304,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.emotional._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth._default.emotional[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.emotional._default[2]</t>
+          <t xml:space="preserve">pop_growth._default.emotional[2]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="10">
@@ -2336,7 +2336,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.normal[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal._default[1]</t>
+          <t xml:space="preserve">pop_star._default.normal[1]</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="5">
@@ -2368,7 +2368,7 @@
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.normal[2]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal._default[2]</t>
+          <t xml:space="preserve">pop_star._default.normal[2]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="5">
@@ -2400,7 +2400,7 @@
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.bold[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold._default[1]</t>
+          <t xml:space="preserve">pop_star._default.bold[1]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="6">
@@ -2432,7 +2432,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.bold[2]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold._default[2]</t>
+          <t xml:space="preserve">pop_star._default.bold[2]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="6">
@@ -2464,7 +2464,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.quiet._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.quiet[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.quiet._default[1]</t>
+          <t xml:space="preserve">pop_star._default.quiet[1]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="7">
@@ -2496,7 +2496,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.easygoing._default[1]</t>
+          <t xml:space="preserve">pop_star._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="9">
@@ -2528,7 +2528,7 @@
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.earnest._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.earnest[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.earnest._default[1]</t>
+          <t xml:space="preserve">pop_star._default.earnest[1]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="10">
@@ -2560,7 +2560,7 @@
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.earnest._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.earnest[2]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.earnest._default[2]</t>
+          <t xml:space="preserve">pop_star._default.earnest[2]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="10">
@@ -2592,7 +2592,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.emotional._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.emotional[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.emotional._default[1]</t>
+          <t xml:space="preserve">pop_star._default.emotional[1]</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="10">
@@ -2624,7 +2624,7 @@
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.emotional._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star._default.emotional[2]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.emotional._default[2]</t>
+          <t xml:space="preserve">pop_star._default.emotional[2]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="10">
@@ -2656,7 +2656,7 @@
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.normal[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal._default[1]</t>
+          <t xml:space="preserve">cap_reached._default.normal[1]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="5">
@@ -2688,7 +2688,7 @@
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.normal[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal._default[2]</t>
+          <t xml:space="preserve">cap_reached._default.normal[2]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="5">
@@ -2720,7 +2720,7 @@
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.bold[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold._default[1]</t>
+          <t xml:space="preserve">cap_reached._default.bold[1]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="6">
@@ -2752,7 +2752,7 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.bold[2]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold._default[2]</t>
+          <t xml:space="preserve">cap_reached._default.bold[2]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="6">
@@ -2784,7 +2784,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.quiet._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.quiet[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.quiet._default[1]</t>
+          <t xml:space="preserve">cap_reached._default.quiet[1]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="7">
@@ -2816,7 +2816,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.easygoing._default[1]</t>
+          <t xml:space="preserve">cap_reached._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="9">
@@ -2848,7 +2848,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.earnest._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.earnest[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.earnest._default[1]</t>
+          <t xml:space="preserve">cap_reached._default.earnest[1]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="10">
@@ -2880,7 +2880,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.earnest._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.earnest[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.earnest._default[2]</t>
+          <t xml:space="preserve">cap_reached._default.earnest[2]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="10">
@@ -2912,7 +2912,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.emotional._default[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.emotional[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.emotional._default[1]</t>
+          <t xml:space="preserve">cap_reached._default.emotional[1]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="10">
@@ -2944,7 +2944,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.emotional._default[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached._default.emotional[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.emotional._default[2]</t>
+          <t xml:space="preserve">cap_reached._default.emotional[2]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="10">
@@ -2976,7 +2976,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.normal[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal._default[1]</t>
+          <t xml:space="preserve">defeat._default.normal[1]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="5">
@@ -3008,7 +3008,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal._default[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.normal[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal._default[2]</t>
+          <t xml:space="preserve">defeat._default.normal[2]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="5">
@@ -3040,7 +3040,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.bold[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold._default[1]</t>
+          <t xml:space="preserve">defeat._default.bold[1]</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="6">
@@ -3072,7 +3072,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold._default[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.bold[2]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold._default[2]</t>
+          <t xml:space="preserve">defeat._default.bold[2]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="6">
@@ -3104,7 +3104,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.quiet[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.quiet._default[1]</t>
+          <t xml:space="preserve">defeat._default.quiet[1]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="7">
@@ -3136,7 +3136,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.shy._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.shy[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.shy._default[1]</t>
+          <t xml:space="preserve">defeat._default.shy[1]</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="8">
@@ -3168,7 +3168,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing._default[1]</t>
+          <t xml:space="preserve">defeat._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="9">
@@ -3200,7 +3200,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.earnest[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest._default[1]</t>
+          <t xml:space="preserve">defeat._default.earnest[1]</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="10">
@@ -3232,7 +3232,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest._default[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.earnest[2]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest._default[2]</t>
+          <t xml:space="preserve">defeat._default.earnest[2]</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="10">
@@ -3264,7 +3264,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.emotional._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.emotional[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.emotional._default[1]</t>
+          <t xml:space="preserve">defeat._default.emotional[1]</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="10">
@@ -3296,7 +3296,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.emotional._default[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat._default.emotional[2]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.emotional._default[2]</t>
+          <t xml:space="preserve">defeat._default.emotional[2]</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="10">
@@ -3328,7 +3328,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery._default.normal[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal._default[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery._default.normal[1]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="5">
@@ -3360,7 +3360,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal._default[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery._default.normal[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal._default[2]</t>
+          <t xml:space="preserve">injury_moderate_recovery._default.normal[2]</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="5">
@@ -3392,7 +3392,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery._default.bold[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.bold._default[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery._default.bold[1]</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="6">
@@ -3424,7 +3424,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.quiet._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery._default.quiet[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.quiet._default[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery._default.quiet[1]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="7">
@@ -3456,7 +3456,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.shy._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery._default.shy[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.shy._default[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery._default.shy[1]</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="8">
@@ -3488,7 +3488,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.easygoing._default[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="9">
@@ -3520,7 +3520,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery._default.earnest[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest._default[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery._default.earnest[1]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="10">
@@ -3552,7 +3552,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.emotional._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery._default.emotional[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.emotional._default[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery._default.emotional[1]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="10">
@@ -3584,7 +3584,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery._default.normal[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal._default[1]</t>
+          <t xml:space="preserve">injury_severe_recovery._default.normal[1]</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="5">
@@ -3616,7 +3616,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal._default[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery._default.normal[2]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal._default[2]</t>
+          <t xml:space="preserve">injury_severe_recovery._default.normal[2]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="5">
@@ -3648,7 +3648,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery._default.bold[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.bold._default[1]</t>
+          <t xml:space="preserve">injury_severe_recovery._default.bold[1]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="6">
@@ -3680,7 +3680,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.quiet._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery._default.quiet[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.quiet._default[1]</t>
+          <t xml:space="preserve">injury_severe_recovery._default.quiet[1]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="7">
@@ -3712,7 +3712,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.shy._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery._default.shy[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.shy._default[1]</t>
+          <t xml:space="preserve">injury_severe_recovery._default.shy[1]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="8">
@@ -3744,7 +3744,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.easygoing._default[1]</t>
+          <t xml:space="preserve">injury_severe_recovery._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="9">
@@ -3776,7 +3776,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery._default.earnest[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest._default[1]</t>
+          <t xml:space="preserve">injury_severe_recovery._default.earnest[1]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="10">
@@ -3808,7 +3808,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.emotional._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery._default.emotional[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.emotional._default[1]</t>
+          <t xml:space="preserve">injury_severe_recovery._default.emotional[1]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="10">
@@ -3840,7 +3840,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end._default.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal._default[1]</t>
+          <t xml:space="preserve">penalty_end._default.normal[1]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="5">
@@ -3872,7 +3872,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal._default[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end._default.normal[2]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal._default[2]</t>
+          <t xml:space="preserve">penalty_end._default.normal[2]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="5">
@@ -3904,7 +3904,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end._default.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.bold._default[1]</t>
+          <t xml:space="preserve">penalty_end._default.bold[1]</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="6">
@@ -3936,7 +3936,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.quiet._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end._default.quiet[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.quiet._default[1]</t>
+          <t xml:space="preserve">penalty_end._default.quiet[1]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="7">
@@ -3968,7 +3968,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.shy._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end._default.shy[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.shy._default[1]</t>
+          <t xml:space="preserve">penalty_end._default.shy[1]</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="8">
@@ -4000,7 +4000,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.easygoing._default[1]</t>
+          <t xml:space="preserve">penalty_end._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="9">
@@ -4032,7 +4032,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end._default.earnest[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest._default[1]</t>
+          <t xml:space="preserve">penalty_end._default.earnest[1]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="10">
@@ -4064,7 +4064,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.emotional._default[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end._default.emotional[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.emotional._default[1]</t>
+          <t xml:space="preserve">penalty_end._default.emotional[1]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="10">
@@ -4096,7 +4096,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal._default[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="5">
@@ -4128,7 +4128,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal._default[2]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="5">
@@ -4160,7 +4160,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold._default[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="6">
@@ -4192,7 +4192,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="7">
@@ -4224,7 +4224,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.shy._default[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="8">
@@ -4256,7 +4256,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="9">
@@ -4288,7 +4288,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="10">
@@ -4320,7 +4320,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="10">
@@ -4352,7 +4352,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="10">
@@ -4384,7 +4384,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="5">
@@ -4416,7 +4416,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal._default[2]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="5">
@@ -4448,7 +4448,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="6">
@@ -4480,7 +4480,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="7">
@@ -4512,7 +4512,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.shy._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="8">
@@ -4544,7 +4544,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="9">
@@ -4576,7 +4576,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="10">
@@ -4608,7 +4608,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="10">
@@ -4640,7 +4640,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="10">
@@ -4672,7 +4672,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="10">
@@ -4704,7 +4704,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.normal._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh._default.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.normal._default[1]</t>
+          <t xml:space="preserve">fresh._default.normal[1]</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="5">
@@ -4736,7 +4736,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.bold._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh._default.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.bold._default[1]</t>
+          <t xml:space="preserve">fresh._default.bold[1]</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="6">
@@ -4768,7 +4768,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.easygoing._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.easygoing._default[1]</t>
+          <t xml:space="preserve">fresh._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="9">
@@ -4800,7 +4800,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.earnest._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh._default.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.earnest._default[1]</t>
+          <t xml:space="preserve">fresh._default.earnest[1]</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="10">
@@ -4832,7 +4832,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.emotional._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh._default.emotional[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.emotional._default[1]</t>
+          <t xml:space="preserve">fresh._default.emotional[1]</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="10">
@@ -4864,7 +4864,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.quiet._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh._default.quiet[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.quiet._default[1]</t>
+          <t xml:space="preserve">fresh._default.quiet[1]</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="7">
@@ -4896,7 +4896,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.shy._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh._default.shy[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.shy._default[1]</t>
+          <t xml:space="preserve">fresh._default.shy[1]</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="8">
@@ -4928,7 +4928,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.normal._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm._default.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.normal._default[1]</t>
+          <t xml:space="preserve">warm._default.normal[1]</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="5">
@@ -4960,7 +4960,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.bold._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm._default.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.bold._default[1]</t>
+          <t xml:space="preserve">warm._default.bold[1]</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="6">
@@ -4992,7 +4992,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.easygoing._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.easygoing._default[1]</t>
+          <t xml:space="preserve">warm._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="9">
@@ -5024,7 +5024,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.earnest._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm._default.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.earnest._default[1]</t>
+          <t xml:space="preserve">warm._default.earnest[1]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="10">
@@ -5056,7 +5056,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.emotional._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm._default.emotional[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.emotional._default[1]</t>
+          <t xml:space="preserve">warm._default.emotional[1]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="10">
@@ -5088,7 +5088,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.quiet._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm._default.quiet[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.quiet._default[1]</t>
+          <t xml:space="preserve">warm._default.quiet[1]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="7">
@@ -5120,7 +5120,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.shy._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm._default.shy[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.shy._default[1]</t>
+          <t xml:space="preserve">warm._default.shy[1]</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="8">
@@ -5152,7 +5152,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.normal._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy._default.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.normal._default[1]</t>
+          <t xml:space="preserve">heavy._default.normal[1]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="5">
@@ -5184,7 +5184,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.bold._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy._default.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.bold._default[1]</t>
+          <t xml:space="preserve">heavy._default.bold[1]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="6">
@@ -5216,7 +5216,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.easygoing._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.easygoing._default[1]</t>
+          <t xml:space="preserve">heavy._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="9">
@@ -5248,7 +5248,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.earnest._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy._default.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.earnest._default[1]</t>
+          <t xml:space="preserve">heavy._default.earnest[1]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="10">
@@ -5280,7 +5280,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.emotional._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy._default.emotional[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.emotional._default[1]</t>
+          <t xml:space="preserve">heavy._default.emotional[1]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="10">
@@ -5312,7 +5312,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.quiet._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy._default.quiet[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.quiet._default[1]</t>
+          <t xml:space="preserve">heavy._default.quiet[1]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="7">
@@ -5344,7 +5344,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.shy._default[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy._default.shy[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.shy._default[1]</t>
+          <t xml:space="preserve">heavy._default.shy[1]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="8">
@@ -5376,7 +5376,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="5">
@@ -5408,7 +5408,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal._default[2]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="5">
@@ -5440,7 +5440,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="6">
@@ -5472,7 +5472,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="7">
@@ -5504,7 +5504,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.shy._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="8">
@@ -5536,7 +5536,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="9">
@@ -5568,7 +5568,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="10">
@@ -5600,7 +5600,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="10">
